--- a/Resultados/df_resultados_finales.xlsx
+++ b/Resultados/df_resultados_finales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\Python Script\Github\IBNR-NIIF-17\Resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Python_script\Github\IBNR-NIIF-17\Resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D91CC5E-9EFD-4A9D-80B3-1936388C5618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80398A50-ADB5-4C1A-83A8-52CA64FE9DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -499,101 +499,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:R37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="30" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="40" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C1" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>434.22568943619632</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+        <v>262.6662462180185</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2266.9195792784271</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+        <v>1268.465199104774</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>169.95478140006361</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+        <v>92.838994924973164</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>422.74160762946559</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+        <v>260.59927012577577</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>1879.796491475937</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+        <v>1090.52243676272</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7">
-        <v>134.39373579897079</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+        <v>76.628332711201551</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8">
-        <v>538.57073568454507</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+        <v>376.03605580868219</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9">
-        <v>1053.0508897497571</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+        <v>662.85366922437549</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10">
-        <v>67.752971946354407</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+        <v>42.519024501616528</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
@@ -607,52 +607,52 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="3">
-        <v>434.22568943619632</v>
+        <v>262.6662462180185</v>
       </c>
       <c r="D21" s="3">
-        <v>422.74160762946559</v>
+        <v>260.59927012577577</v>
       </c>
       <c r="E21" s="3">
         <f>D21-C21</f>
-        <v>-11.484081806730728</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+        <v>-2.0669760922427258</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="3">
-        <v>2266.9195792784271</v>
+        <v>1268.465199104774</v>
       </c>
       <c r="D22" s="3">
-        <v>1879.796491475937</v>
+        <v>1090.52243676272</v>
       </c>
       <c r="E22" s="3">
         <f>D22-C22</f>
-        <v>-387.12308780249009</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+        <v>-177.94276234205404</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="3">
-        <v>169.95478140006361</v>
+        <v>92.838994924973164</v>
       </c>
       <c r="D23" s="3">
-        <v>134.39373579897079</v>
+        <v>76.628332711201551</v>
       </c>
       <c r="E23" s="3">
         <f>D23-C23</f>
-        <v>-35.561045601092815</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+        <v>-16.210662213771613</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N24" s="1" t="s">
         <v>9</v>
       </c>
@@ -666,55 +666,55 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O25" s="3">
         <f>SUM(O30:P30)</f>
-        <v>422.74160762946559</v>
+        <v>260.59927012577577</v>
       </c>
       <c r="P25" s="4">
-        <v>0.38713297747588221</v>
+        <v>0.42475268932774846</v>
       </c>
       <c r="Q25" s="3">
         <f>P25*O25</f>
-        <v>163.65721726453614</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+        <v>110.69024082277164</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="O26" s="3">
         <f>SUM(O31:P31)</f>
-        <v>1879.796491475937</v>
+        <v>1090.52243676272</v>
       </c>
       <c r="P26" s="4">
-        <v>0.14874520584066048</v>
+        <v>0.17137788792876438</v>
       </c>
       <c r="Q26" s="3">
         <f t="shared" ref="Q26:Q27" si="0">P26*O26</f>
-        <v>279.61071606313965</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+        <v>186.89143195132445</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="O27" s="3">
         <f>SUM(O32:P32)</f>
-        <v>134.39373579897079</v>
+        <v>76.628332711201551</v>
       </c>
       <c r="P27" s="4">
-        <v>0.25479113781598445</v>
+        <v>0.27966835118383288</v>
       </c>
       <c r="Q27" s="3">
         <f t="shared" si="0"/>
-        <v>34.24233285956057</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+        <v>21.430519463307903</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N29" s="1" t="s">
         <v>9</v>
       </c>
@@ -731,70 +731,70 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O30" s="3">
         <f>C21</f>
-        <v>434.22568943619632</v>
+        <v>262.6662462180185</v>
       </c>
       <c r="P30" s="3">
         <f>E21</f>
-        <v>-11.484081806730728</v>
+        <v>-2.0669760922427258</v>
       </c>
       <c r="Q30" s="3">
         <f>D21*$P$25</f>
-        <v>163.65721726453614</v>
+        <v>110.69024082277164</v>
       </c>
       <c r="R30" s="3">
         <f>SUM(O30:Q30)</f>
-        <v>586.39882489400179</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
+        <v>371.28951094854744</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="O31" s="3">
         <f>C22</f>
-        <v>2266.9195792784271</v>
+        <v>1268.465199104774</v>
       </c>
       <c r="P31" s="3">
         <f>E22</f>
-        <v>-387.12308780249009</v>
+        <v>-177.94276234205404</v>
       </c>
       <c r="Q31" s="3">
         <f>D22*$P$26</f>
-        <v>279.61071606313965</v>
+        <v>186.89143195132445</v>
       </c>
       <c r="R31" s="3">
         <f>SUM(O31:Q31)</f>
-        <v>2159.4072075390768</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
+        <v>1277.4138687140444</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N32" s="1" t="s">
         <v>13</v>
       </c>
       <c r="O32" s="3">
         <f>C23</f>
-        <v>169.95478140006361</v>
+        <v>92.838994924973164</v>
       </c>
       <c r="P32" s="3">
         <f>E23</f>
-        <v>-35.561045601092815</v>
+        <v>-16.210662213771613</v>
       </c>
       <c r="Q32" s="3">
         <f>D23*$P$27</f>
-        <v>34.24233285956057</v>
+        <v>21.430519463307903</v>
       </c>
       <c r="R32" s="3">
         <f>SUM(O32:Q32)</f>
-        <v>168.63606865853137</v>
-      </c>
-    </row>
-    <row r="34" spans="14:15" x14ac:dyDescent="0.3">
+        <v>98.058852174509454</v>
+      </c>
+    </row>
+    <row r="34" spans="14:17" x14ac:dyDescent="0.25">
       <c r="N34" s="1" t="s">
         <v>9</v>
       </c>
@@ -802,27 +802,45 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="14:17" x14ac:dyDescent="0.25">
       <c r="N35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O35" s="3">
+        <v>376.03605580868219</v>
+      </c>
+      <c r="P35">
+        <v>376.03605580868219</v>
+      </c>
+      <c r="Q35">
         <v>538.57073568454507</v>
       </c>
     </row>
-    <row r="36" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="14:17" x14ac:dyDescent="0.25">
       <c r="N36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="O36" s="3">
+        <v>662.85366922437549</v>
+      </c>
+      <c r="P36">
+        <v>662.85366922437549</v>
+      </c>
+      <c r="Q36">
         <v>1053.0508897497571</v>
       </c>
     </row>
-    <row r="37" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="14:17" x14ac:dyDescent="0.25">
       <c r="N37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="O37" s="3">
+        <v>42.519024501616535</v>
+      </c>
+      <c r="P37">
+        <v>42.519024501616535</v>
+      </c>
+      <c r="Q37">
         <v>67.752971946354407</v>
       </c>
     </row>
